--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Force_EndstopNL.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Force_EndstopNL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Dampers\Damper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA758F5-F76F-4EB2-9F1C-68CC4C90976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D00256-0526-4BE7-B267-53CECAE6BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="967" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
+    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="967" activeTab="2" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
   </bookViews>
   <sheets>
     <sheet name="SUV_Landy_TA2PR_f" sheetId="23" r:id="rId1"/>
@@ -702,13 +702,13 @@
         <v>14</v>
       </c>
       <c r="F5" s="19">
-        <v>-1.5900000000000001E-2</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="G5" s="19">
-        <v>0.50453999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="H5" s="19">
-        <v>0.62</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>14</v>
@@ -732,13 +732,13 @@
         <v>14</v>
       </c>
       <c r="F6" s="19">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G6" s="19">
-        <v>0.50453999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H6" s="19">
-        <v>0.5</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>14</v>
@@ -1220,14 +1220,13 @@
         <v>14</v>
       </c>
       <c r="F5" s="19">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G5" s="19">
-        <v>0.48549999999999999</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="H5" s="19">
-        <v>0.67633500000000002</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>14</v>
@@ -1249,14 +1248,13 @@
         <v>14</v>
       </c>
       <c r="F6" s="19">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G6" s="19">
-        <v>0.48549999999999999</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H6" s="19">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>14</v>
@@ -1282,25 +1280,25 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="13">
-        <v>-0.13500000000000001</v>
+        <v>-0.17799999999999999</v>
       </c>
       <c r="I7" s="13">
-        <v>-0.13</v>
+        <v>-0.17299999999999999</v>
       </c>
       <c r="J7" s="13">
-        <v>-0.125</v>
+        <v>-0.16800000000000001</v>
       </c>
       <c r="K7" s="17">
-        <v>-0.115</v>
+        <v>-0.158</v>
       </c>
       <c r="L7" s="13">
         <v>0</v>
       </c>
       <c r="M7" s="17">
-        <v>0.13500000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="N7" s="13">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">

--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Force_EndstopNL.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Force_EndstopNL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Dampers\Damper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D00256-0526-4BE7-B267-53CECAE6BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91CFCA4-B800-40DD-9624-909AE993455A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="967" activeTab="2" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
+    <workbookView xWindow="31320" yWindow="2100" windowWidth="25485" windowHeight="11340" tabRatio="967" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
   </bookViews>
   <sheets>
     <sheet name="SUV_Landy_TA2PR_f" sheetId="23" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="23">
   <si>
     <t>Units</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>SUV_Landy_TA4Watts_ForceEndstopNL_A2</t>
+  </si>
+  <si>
+    <t>Should be consistent with values in Linkage</t>
   </si>
 </sst>
 </file>
@@ -184,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -221,6 +224,7 @@
     <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,7 +620,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
@@ -626,9 +630,10 @@
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="9" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -648,7 +653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -661,7 +666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -673,7 +678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -687,7 +692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -719,7 +724,7 @@
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
@@ -749,7 +754,7 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -760,8 +765,8 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
+      <c r="E7" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -786,8 +791,9 @@
       <c r="N7" s="13">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="20"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="13" t="s">
         <v>16</v>
@@ -796,56 +802,57 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8">
+      <c r="H8" s="13">
         <v>-13000</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="13">
         <v>-11000</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="13">
         <v>-5000</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <v>40000</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="20"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="H9" s="15"/>
-      <c r="J9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="14"/>
       <c r="H10" s="15"/>
       <c r="J10" s="13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A10">
@@ -867,7 +874,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="14" customWidth="1"/>
@@ -877,11 +884,11 @@
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="10" max="15" width="7" customWidth="1"/>
+    <col min="16" max="16" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -901,7 +908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -914,7 +921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -926,7 +933,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -940,7 +947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -957,21 +964,23 @@
       <c r="F5" s="18">
         <v>-2.6557142857142869E-3</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="18">
         <f>0.62-0.25</f>
         <v>0.37</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="18">
         <v>0.65</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
@@ -986,21 +995,23 @@
       <c r="F6" s="18">
         <v>5.5166428571428582E-2</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="18">
         <f>0.85-0.25</f>
         <v>0.6</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="18">
         <v>0.19</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -1011,8 +1022,8 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
+      <c r="E7" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1038,7 +1049,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="13" t="s">
         <v>16</v>
@@ -1047,62 +1058,64 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8">
+      <c r="H8" s="13">
         <v>-13000</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="13">
         <v>-11000</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="13">
         <v>-5000</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="H9" s="15"/>
-      <c r="J9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="14"/>
       <c r="H10" s="15"/>
       <c r="J10" s="13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="20"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J11" s="20"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="14"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="14"/>
       <c r="H14" s="15"/>
     </row>
@@ -1142,8 +1155,7 @@
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="10" max="15" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1231,9 +1243,11 @@
       <c r="J5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
@@ -1259,9 +1273,11 @@
       <c r="J6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1274,8 +1290,8 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
+      <c r="E7" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1310,56 +1326,56 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8">
+      <c r="H8" s="13">
         <v>-13000</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="13">
         <v>-11000</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="13">
         <v>-5000</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <v>40000</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="H9" s="15"/>
-      <c r="J9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="14"/>
       <c r="H10" s="15"/>
       <c r="J10" s="13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J11" s="20"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13" s="14"/>
@@ -1408,8 +1424,7 @@
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+    <col min="10" max="15" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1498,9 +1513,11 @@
       <c r="J5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
@@ -1526,9 +1543,11 @@
       <c r="J6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1541,8 +1560,8 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
+      <c r="E7" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1577,56 +1596,56 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
+      <c r="E8" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8">
+      <c r="H8" s="13">
         <v>-13000</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="13">
         <v>-11000</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="13">
         <v>-5000</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <v>40000</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="H9" s="15"/>
-      <c r="J9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="14"/>
       <c r="H10" s="15"/>
       <c r="J10" s="13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J11" s="20"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13" s="14"/>
